--- a/data/trans_dic/P14B23-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P14B23-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con enfermedades crónicas discapacitantes de salud mental (trastornos depresivos o ansiedad)</t>
+          <t>Población cuya depresión o ansiedad le limita (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,73</t>
+          <t>0,0; 0,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,9</t>
+          <t>0,0; 1,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 5,95</t>
+          <t>0,74; 6,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,39</t>
+          <t>0,0; 1,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,7</t>
+          <t>1,0; 4,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 8,13</t>
+          <t>1,58; 8,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,86</t>
+          <t>0,09; 0,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,49</t>
+          <t>0,74; 2,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 5,31</t>
+          <t>1,48; 5,37</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,57</t>
+          <t>0,28; 1,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,98</t>
+          <t>0,0; 1,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,27</t>
+          <t>0,26; 2,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,44</t>
+          <t>1,58; 4,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,28</t>
+          <t>0,41; 2,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 6,06</t>
+          <t>2,27; 6,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,65</t>
+          <t>1,01; 2,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,3</t>
+          <t>0,33; 1,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,95</t>
+          <t>1,58; 3,89</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 5,52</t>
+          <t>2,29; 5,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,9</t>
+          <t>0,84; 2,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,68; 6,49</t>
+          <t>2,67; 6,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,86; 8,88</t>
+          <t>4,92; 8,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,7; 5,49</t>
+          <t>2,7; 5,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,2; 6,23</t>
+          <t>3,05; 6,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,04; 6,6</t>
+          <t>4,01; 6,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 3,78</t>
+          <t>2,03; 3,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,28; 5,64</t>
+          <t>3,34; 5,77</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,27</t>
+          <t>1,38; 4,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,54</t>
+          <t>1,76; 4,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,89</t>
+          <t>1,63; 5,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,61; 9,97</t>
+          <t>5,84; 10,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,8; 10,18</t>
+          <t>5,92; 10,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,37; 9,8</t>
+          <t>6,3; 9,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,9; 6,61</t>
+          <t>3,8; 6,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,22; 6,84</t>
+          <t>4,24; 6,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,3; 7,13</t>
+          <t>3,54; 7,25</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,64; 6,53</t>
+          <t>2,61; 6,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,23; 5,94</t>
+          <t>2,21; 5,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,09; 7,74</t>
+          <t>4,13; 7,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,32; 16,92</t>
+          <t>10,35; 17,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,85; 14,64</t>
+          <t>8,56; 14,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,71; 13,8</t>
+          <t>9,75; 13,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,17; 11,11</t>
+          <t>7,24; 11,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,97; 9,46</t>
+          <t>5,99; 9,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,36; 10,13</t>
+          <t>7,22; 10,11</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,94; 6,58</t>
+          <t>1,98; 6,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,65</t>
+          <t>0,28; 2,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,84</t>
+          <t>1,81; 4,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,45; 18,97</t>
+          <t>11,35; 18,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,3; 14,87</t>
+          <t>8,47; 15,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,79; 10,98</t>
+          <t>2,8; 11,04</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,61; 12,3</t>
+          <t>7,6; 12,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,93; 8,66</t>
+          <t>4,9; 8,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,93; 7,36</t>
+          <t>2,67; 7,36</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,66; 7,74</t>
+          <t>1,69; 7,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,2; 6,51</t>
+          <t>1,95; 6,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,18; 7,65</t>
+          <t>3,3; 7,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,01; 19,85</t>
+          <t>11,96; 19,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,71; 15,92</t>
+          <t>8,33; 15,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,06; 13,27</t>
+          <t>8,9; 13,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,5; 13,58</t>
+          <t>8,24; 13,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,4; 11,14</t>
+          <t>6,28; 11,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,1; 10,36</t>
+          <t>7,09; 10,33</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,99; 3,15</t>
+          <t>1,98; 3,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,51</t>
+          <t>1,52; 2,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,81; 4,42</t>
+          <t>2,76; 4,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,13; 9,01</t>
+          <t>7,1; 8,96</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,87; 7,57</t>
+          <t>5,83; 7,57</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,78; 8,09</t>
+          <t>5,86; 8,11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,79; 5,83</t>
+          <t>4,83; 5,95</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,9; 4,91</t>
+          <t>3,94; 4,91</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,8; 6,09</t>
+          <t>4,81; 6,15</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con enfermedades crónicas discapacitantes de salud mental (trastornos depresivos o ansiedad)</t>
+          <t>Población cuya depresión o ansiedad le limita (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3314</t>
+          <t>0; 3871</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 7990</t>
+          <t>0; 7915</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2462; 23780</t>
+          <t>2943; 27330</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5981</t>
+          <t>0; 6999</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4597; 18603</t>
+          <t>3950; 18254</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5632; 25464</t>
+          <t>4938; 25332</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>815; 7583</t>
+          <t>820; 8610</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5672; 20302</t>
+          <t>6024; 21809</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10963; 37846</t>
+          <t>10531; 38272</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1886; 10772</t>
+          <t>1907; 11478</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5815</t>
+          <t>0; 7663</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1050; 9631</t>
+          <t>1111; 9286</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9747; 27103</t>
+          <t>9619; 26778</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2743; 12843</t>
+          <t>2334; 13488</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10205; 31048</t>
+          <t>11604; 32185</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14124; 34336</t>
+          <t>13106; 32980</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3721; 14999</t>
+          <t>3767; 15840</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15199; 36913</t>
+          <t>14766; 36373</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15212; 37611</t>
+          <t>15604; 37221</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5718; 19428</t>
+          <t>5590; 19231</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14353; 34829</t>
+          <t>14345; 34183</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34417; 62847</t>
+          <t>34788; 62473</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>17844; 36304</t>
+          <t>17825; 37207</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18963; 36900</t>
+          <t>18048; 36059</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>56190; 91737</t>
+          <t>55786; 89247</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>26741; 50272</t>
+          <t>27017; 49892</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>37019; 63582</t>
+          <t>37669; 65107</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9000; 26242</t>
+          <t>8473; 25872</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12222; 29304</t>
+          <t>11390; 29943</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14240; 52302</t>
+          <t>14490; 51137</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>34309; 60999</t>
+          <t>35724; 61819</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>37673; 66108</t>
+          <t>38431; 66888</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>45409; 69883</t>
+          <t>44904; 69752</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>47826; 81052</t>
+          <t>46650; 79439</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>54662; 88553</t>
+          <t>54940; 87135</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52849; 114149</t>
+          <t>56651; 116099</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11331; 28056</t>
+          <t>11190; 28462</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10652; 28385</t>
+          <t>10561; 28317</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22939; 43414</t>
+          <t>23159; 43630</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46124; 75592</t>
+          <t>46268; 76265</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>43952; 72741</t>
+          <t>42509; 71580</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>53186; 75632</t>
+          <t>53420; 75787</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>62857; 97364</t>
+          <t>63435; 97727</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>58200; 92207</t>
+          <t>58386; 94837</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>81670; 112380</t>
+          <t>80031; 112127</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5990; 20313</t>
+          <t>6107; 20150</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>927; 8857</t>
+          <t>936; 8923</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6696; 17822</t>
+          <t>6664; 17558</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>40546; 67159</t>
+          <t>40178; 66907</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>31372; 56185</t>
+          <t>32008; 56859</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16994; 66828</t>
+          <t>17023; 67142</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>50442; 81494</t>
+          <t>50378; 80756</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>35138; 61662</t>
+          <t>34857; 61741</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>28632; 71833</t>
+          <t>26088; 71841</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4133; 19247</t>
+          <t>4216; 18565</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5643; 16725</t>
+          <t>5015; 15940</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8982; 21628</t>
+          <t>9325; 20998</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>46340; 76576</t>
+          <t>46149; 74974</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>34837; 63700</t>
+          <t>33353; 62274</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>38585; 56528</t>
+          <t>37908; 56297</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>53916; 86175</t>
+          <t>52314; 84622</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>42065; 73224</t>
+          <t>41249; 72948</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>50276; 73422</t>
+          <t>50255; 73221</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>68163; 107992</t>
+          <t>67656; 107473</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>53009; 85211</t>
+          <t>51745; 84366</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>97311; 153069</t>
+          <t>95568; 151131</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>253008; 319642</t>
+          <t>251793; 317833</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>208193; 268155</t>
+          <t>206790; 268244</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>214393; 300328</t>
+          <t>217540; 301198</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>333642; 406157</t>
+          <t>336930; 414637</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>270864; 340407</t>
+          <t>273416; 340593</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>344408; 437020</t>
+          <t>345309; 440752</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P14B23-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P14B23-Edad-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,85</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,89</t>
+          <t>0,0; 1,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,83</t>
+          <t>0,62; 5,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 1,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,61</t>
+          <t>1,01; 4,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 8,09</t>
+          <t>1,51; 6,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,97</t>
+          <t>0,09; 0,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,68</t>
+          <t>0,71; 2,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 5,37</t>
+          <t>1,41; 4,83</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,67</t>
+          <t>0,28; 1,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,3</t>
+          <t>0,0; 1,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,19</t>
+          <t>0,54; 3,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,39</t>
+          <t>1,62; 4,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,39</t>
+          <t>0,35; 2,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,27; 6,29</t>
+          <t>2,68; 7,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,54</t>
+          <t>1,08; 2,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,37</t>
+          <t>0,33; 1,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,89</t>
+          <t>1,98; 4,35</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,46</t>
+          <t>2,13; 5,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,87</t>
+          <t>0,8; 2,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,67; 6,37</t>
+          <t>2,41; 6,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,92; 8,83</t>
+          <t>5,12; 8,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,7; 5,63</t>
+          <t>2,75; 5,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,05; 6,09</t>
+          <t>4,01; 6,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,01; 6,42</t>
+          <t>4,03; 6,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,75</t>
+          <t>2,02; 3,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,34; 5,77</t>
+          <t>3,51; 5,73</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,21</t>
+          <t>1,47; 4,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,63</t>
+          <t>1,89; 4,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 5,76</t>
+          <t>3,4; 7,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,84; 10,1</t>
+          <t>5,72; 10,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,92; 10,31</t>
+          <t>5,82; 10,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,3; 9,78</t>
+          <t>6,84; 9,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,8; 6,48</t>
+          <t>3,88; 6,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,24; 6,73</t>
+          <t>4,26; 6,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,54; 7,25</t>
+          <t>5,62; 8,04</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,61; 6,63</t>
+          <t>2,72; 6,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,21; 5,93</t>
+          <t>2,3; 5,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,13; 7,77</t>
+          <t>3,92; 7,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,35; 17,07</t>
+          <t>10,26; 16,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,56; 14,41</t>
+          <t>8,81; 14,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,75; 13,83</t>
+          <t>9,97; 13,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,24; 11,15</t>
+          <t>6,98; 10,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,99; 9,73</t>
+          <t>5,91; 9,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,22; 10,11</t>
+          <t>7,45; 10,17</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,98; 6,53</t>
+          <t>1,7; 6,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,67</t>
+          <t>0,3; 2,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,77</t>
+          <t>1,71; 4,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,35; 18,9</t>
+          <t>11,14; 18,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,47; 15,05</t>
+          <t>8,58; 15,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,8; 11,04</t>
+          <t>8,31; 12,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,6; 12,19</t>
+          <t>7,49; 12,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,9; 8,67</t>
+          <t>4,94; 8,77</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,67; 7,36</t>
+          <t>5,55; 8,08</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,69; 7,46</t>
+          <t>1,73; 7,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,95; 6,2</t>
+          <t>2,26; 6,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,3; 7,43</t>
+          <t>3,38; 7,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,96; 19,43</t>
+          <t>11,87; 18,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,33; 15,56</t>
+          <t>8,36; 15,46</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,9; 13,22</t>
+          <t>9,07; 13,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,24; 13,33</t>
+          <t>8,35; 13,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,28; 11,1</t>
+          <t>6,41; 11,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,09; 10,33</t>
+          <t>7,31; 10,6</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,98; 3,14</t>
+          <t>2,02; 3,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,49</t>
+          <t>1,53; 2,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,76; 4,37</t>
+          <t>3,14; 4,55</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,1; 8,96</t>
+          <t>7,19; 8,96</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,83; 7,57</t>
+          <t>5,87; 7,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,86; 8,11</t>
+          <t>7,28; 8,8</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,83; 5,95</t>
+          <t>4,79; 5,85</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,94; 4,91</t>
+          <t>3,92; 4,97</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,81; 6,15</t>
+          <t>5,43; 6,47</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8754</t>
+          <t>8600</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12361</t>
+          <t>12887</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21115</t>
+          <t>21487</t>
         </is>
       </c>
     </row>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3871</t>
+          <t>0; 4336</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 7915</t>
+          <t>0; 7517</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2943; 27330</t>
+          <t>2519; 20912</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 6999</t>
+          <t>0; 6000</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3950; 18254</t>
+          <t>4014; 16965</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4938; 25332</t>
+          <t>5472; 25011</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>820; 8610</t>
+          <t>817; 7295</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6024; 21809</t>
+          <t>5770; 21466</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10531; 38272</t>
+          <t>10826; 37199</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>6987</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20185</t>
+          <t>22597</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>23776</t>
+          <t>29585</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1907; 11478</t>
+          <t>1901; 10783</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 7663</t>
+          <t>0; 6756</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1111; 9286</t>
+          <t>2562; 16789</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9619; 26778</t>
+          <t>9860; 27334</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2334; 13488</t>
+          <t>1952; 12483</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11604; 32185</t>
+          <t>13472; 35195</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13106; 32980</t>
+          <t>14028; 34523</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3767; 15840</t>
+          <t>3785; 16002</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14766; 36373</t>
+          <t>19374; 42573</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22949</t>
+          <t>23772</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26887</t>
+          <t>32978</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>49836</t>
+          <t>56749</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15604; 37221</t>
+          <t>14511; 36936</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5590; 19231</t>
+          <t>5368; 19551</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14345; 34183</t>
+          <t>14939; 37474</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34788; 62473</t>
+          <t>36202; 62678</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>17825; 37207</t>
+          <t>18160; 35959</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18048; 36059</t>
+          <t>24992; 42845</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55786; 89247</t>
+          <t>56049; 90255</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27017; 49892</t>
+          <t>26896; 50957</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>37669; 65107</t>
+          <t>43645; 71225</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32783</t>
+          <t>34473</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57045</t>
+          <t>62278</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>89829</t>
+          <t>96751</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8473; 25872</t>
+          <t>9032; 25551</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11390; 29943</t>
+          <t>12216; 29135</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14490; 51137</t>
+          <t>23853; 49745</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35724; 61819</t>
+          <t>35013; 62197</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>38431; 66888</t>
+          <t>37786; 65456</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>44904; 69752</t>
+          <t>50387; 73565</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>46650; 79439</t>
+          <t>47615; 79748</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>54940; 87135</t>
+          <t>55146; 87889</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>56651; 116099</t>
+          <t>80825; 115590</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32243</t>
+          <t>33340</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64234</t>
+          <t>71966</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>96477</t>
+          <t>105307</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11190; 28462</t>
+          <t>11685; 28593</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10561; 28317</t>
+          <t>11001; 28462</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23159; 43630</t>
+          <t>23906; 44696</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46268; 76265</t>
+          <t>45849; 74011</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>42509; 71580</t>
+          <t>43796; 71396</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>53420; 75787</t>
+          <t>60686; 83940</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>63435; 97727</t>
+          <t>61148; 96103</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>58386; 94837</t>
+          <t>57566; 92397</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>80031; 112127</t>
+          <t>90725; 123860</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11178</t>
+          <t>11625</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41347</t>
+          <t>45248</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>52524</t>
+          <t>56873</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6107; 20150</t>
+          <t>5247; 20846</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>936; 8923</t>
+          <t>1017; 8973</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6664; 17558</t>
+          <t>6947; 18126</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>40178; 66907</t>
+          <t>39447; 66215</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>32008; 56859</t>
+          <t>32393; 56986</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17023; 67142</t>
+          <t>36482; 55522</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>50378; 80756</t>
+          <t>49647; 81016</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>34857; 61741</t>
+          <t>35189; 62421</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>26088; 71841</t>
+          <t>47006; 68343</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14303</t>
+          <t>16421</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>46372</t>
+          <t>51375</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>60676</t>
+          <t>67796</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4216; 18565</t>
+          <t>4308; 18191</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5015; 15940</t>
+          <t>5802; 16579</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9325; 20998</t>
+          <t>10482; 24022</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>46149; 74974</t>
+          <t>45803; 73176</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>33353; 62274</t>
+          <t>33467; 61865</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>37908; 56297</t>
+          <t>42124; 62785</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>52314; 84622</t>
+          <t>53011; 86549</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>41249; 72948</t>
+          <t>42145; 72898</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>50255; 73221</t>
+          <t>56641; 82162</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>125802</t>
+          <t>135218</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>268431</t>
+          <t>299330</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>394233</t>
+          <t>434548</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>67656; 107473</t>
+          <t>69133; 108333</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>51745; 84366</t>
+          <t>51778; 86034</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>95568; 151131</t>
+          <t>110878; 160747</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>251793; 317833</t>
+          <t>255069; 317908</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>206790; 268244</t>
+          <t>207921; 270549</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>217540; 301198</t>
+          <t>272183; 328950</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>336930; 414637</t>
+          <t>334280; 407596</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>273416; 340593</t>
+          <t>271816; 345097</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>345309; 440752</t>
+          <t>394765; 470025</t>
         </is>
       </c>
     </row>
